--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>184</v>
+        <v>309</v>
       </c>
       <c r="D2">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="D3">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="E3">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D3">
         <v>183</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>426</v>
